--- a/wwwroot/assets/template/Category_Template.xlsx
+++ b/wwwroot/assets/template/Category_Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F36131EA-9658-4B45-9C7A-D07060B9BE76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Categories" sheetId="1" r:id="rId1"/>
@@ -24,9 +25,6 @@
     <t>LIST OF CATEGORIES</t>
   </si>
   <si>
-    <t>Export date: 23/01/2026 21:21:06</t>
-  </si>
-  <si>
     <t>Total categories: 1</t>
   </si>
   <si>
@@ -36,16 +34,19 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Thể thao</t>
-  </si>
-  <si>
-    <t>Truyện về các môn thể thao và đối kháng.</t>
+    <t>Test</t>
+  </si>
+  <si>
+    <t>Welcome to my world!!!</t>
+  </si>
+  <si>
+    <t>Export date: 23/09/2026 21:21:06</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -374,16 +375,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="9.140625" customWidth="1"/>
-    <col min="3" max="3" width="37.28515625" customWidth="1"/>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
+    <col min="1" max="2" width="9.109375" customWidth="1"/>
+    <col min="3" max="3" width="37.33203125" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="23.4" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -391,9 +392,9 @@
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -401,9 +402,9 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -411,20 +412,20 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="B6" t="s">
         <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
